--- a/media/price_lists/fijamom.xlsx
+++ b/media/price_lists/fijamom.xlsx
@@ -505,8 +505,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>950.0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1178.00</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -543,8 +551,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1870.0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2318.80</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -581,8 +597,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1050.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1302.00</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -619,8 +643,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1488.00</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -657,8 +689,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>163.68</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -695,8 +735,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>138.88</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -733,8 +781,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>880.0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1091.20</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -771,8 +827,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2674.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3315.76</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -809,8 +873,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>341.00</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -847,8 +919,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>586.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>726.64</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -885,8 +965,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>758.0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>939.92</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -923,8 +1011,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>887.0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1099.88</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -961,8 +1057,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1058.0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1311.92</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -999,8 +1103,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2860.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3546.40</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1037,8 +1149,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>496.00</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1075,8 +1195,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>429.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>531.96</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1113,8 +1241,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2548.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3159.52</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1151,8 +1287,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3350.0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4154.00</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1189,8 +1333,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3960.0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4910.40</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1227,8 +1379,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5656.0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>7013.44</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1265,8 +1425,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>8437.0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10461.88</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1303,8 +1471,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>10439.0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>12944.36</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1341,8 +1517,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>14729.0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>18263.96</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1379,8 +1563,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>16159.0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>20037.16</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1417,8 +1609,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>18590.0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>23051.60</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1455,8 +1655,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>20020.0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>24824.80</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1493,8 +1701,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>19800.0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>24552.00</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1531,8 +1747,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>1736.00</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1569,8 +1793,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1144.0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1418.56</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1607,8 +1839,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>550.0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>682.00</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1645,8 +1885,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1430.0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1773.20</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1683,8 +1931,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>308.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>381.92</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1721,8 +1977,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1045.0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1295.80</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1759,8 +2023,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>6435.0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>7979.40</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1797,8 +2069,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3960.0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>4910.40</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1835,8 +2115,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1859.0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2305.16</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1873,8 +2161,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1859.0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2305.16</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1911,8 +2207,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1859.0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2305.16</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1949,8 +2253,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2288.0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2837.12</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -1987,8 +2299,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2288.0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2837.12</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2025,8 +2345,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2288.0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2837.12</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2063,8 +2391,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3289.0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4078.36</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2101,8 +2437,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3718.0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4610.32</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2139,8 +2483,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3718.0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4610.32</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2177,8 +2529,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1573.0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1950.52</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2215,8 +2575,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>660.0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>818.40</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2253,8 +2621,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>990.0</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1227.60</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2291,8 +2667,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>275.0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>341.00</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2329,8 +2713,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>16.12</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2367,8 +2759,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>12870.0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>15958.80</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2405,8 +2805,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>163.68</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2443,8 +2851,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>163.68</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2481,8 +2897,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>163.68</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2519,8 +2943,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>264.0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>327.36</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2557,8 +2989,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>11000.0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>13640.00</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2595,8 +3035,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>8075.0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>10013.00</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2633,8 +3081,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>9922.0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>12303.28</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2671,8 +3127,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1316.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1631.84</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2709,8 +3173,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2002.0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2482.48</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2747,8 +3219,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2116.0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2623.84</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2785,8 +3265,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3375.0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>4185.00</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2823,8 +3311,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1430.0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1773.20</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2861,8 +3357,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>110000.0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>136400.00</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2899,8 +3403,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>110000.0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>136400.00</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2937,8 +3449,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>38500.0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>47740.00</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -2975,8 +3495,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>12100.0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>15004.00</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3013,8 +3541,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>6000.0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>7440.00</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3051,8 +3587,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>15000.0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>18600.00</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3089,8 +3633,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1100.0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1364.00</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3127,8 +3679,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>3500.0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>4340.00</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3165,8 +3725,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>250000.0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>310000.00</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3203,8 +3771,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>7000.0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>8680.00</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3241,8 +3817,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2000.0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2480.00</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3279,8 +3863,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24800.00</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3317,8 +3909,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>8000.0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>9920.00</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3355,8 +3955,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2500.0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>3100.00</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3393,8 +4001,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>8500.0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>10540.00</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3431,8 +4047,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>30000.0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>37200.00</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3469,8 +4093,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>40000.0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>49600.00</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3507,8 +4139,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1000.0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1240.00</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3545,8 +4185,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>50000.0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>62000.00</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3583,8 +4231,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>65000.0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>80600.00</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3621,8 +4277,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20000.0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>24800.00</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3659,8 +4323,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>400000.0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>496000.00</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3697,8 +4369,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>76000.0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>94240.00</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3735,8 +4415,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>320000.0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>396800.00</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3773,8 +4461,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>79200.0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>98208.00</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3811,8 +4507,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>280000.0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>347200.00</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3849,8 +4553,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>643500.0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>797940.00</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3887,8 +4599,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>643500.0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>797940.00</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3925,8 +4645,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>643500.0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>797940.00</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -3963,8 +4691,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>643500.0</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>797940.00</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4001,8 +4737,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>643500.0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>797940.00</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4039,8 +4783,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>759330.0</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>941569.20</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4077,8 +4829,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>707850.0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>877734.00</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4115,8 +4875,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>965250.0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1196910.00</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4153,8 +4921,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2574000.0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>3191760.00</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4191,8 +4967,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2059200.0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2553408.00</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4229,8 +5013,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2574000.0</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>3191760.00</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4267,8 +5059,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>836550.0</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1037322.00</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4305,8 +5105,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>965250.0</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1196910.00</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4343,8 +5151,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1544400.0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1915056.00</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4381,8 +5197,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2187900.0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2712996.00</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4419,8 +5243,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1784640.0</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2212953.60</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4457,8 +5289,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2059200.0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2553408.00</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4495,8 +5335,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>3217500.0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>3989700.00</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4533,8 +5381,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2123550.0</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2633202.00</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4571,8 +5427,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>3861000.0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>4787640.00</t>
+        </is>
+      </c>
       <c r="I109" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4609,8 +5473,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2895750.0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>3590730.00</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4647,8 +5519,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>3377660.0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>4188298.40</t>
+        </is>
+      </c>
       <c r="I111" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4685,8 +5565,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>4979260.0</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>6174282.40</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4723,8 +5611,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1673100.0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2074644.00</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4761,8 +5657,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>939510.0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1164992.40</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4799,8 +5703,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1158300.0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1436292.00</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4837,8 +5749,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>3603600.0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>4468464.00</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4875,8 +5795,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>3732300.0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>4628052.00</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4913,8 +5841,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1132560.0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1404374.40</t>
+        </is>
+      </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4951,8 +5887,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1158300.0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1436292.00</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -4989,8 +5933,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1415700.0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1755468.00</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -5027,8 +5979,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1847560.0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2290974.40</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr">
         <is>
           <t>skipped</t>
@@ -5065,8 +6025,16 @@
           <t>1400.0</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1850.0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2294.00</t>
+        </is>
+      </c>
       <c r="I122" t="inlineStr">
         <is>
           <t>skipped</t>

--- a/media/price_lists/fijamom.xlsx
+++ b/media/price_lists/fijamom.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J122"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,45 +436,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>parser_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>price_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>title_original</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_original</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>dollar_rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>price_ars</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>price_wholesale_final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -489,38 +499,44 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>KIT HUECO TARUGO 10</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>950</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>950.0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>1178.00</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -535,38 +551,44 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>KIT CON TARUGOS DEL 12 Y EL 8</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>1870</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>1870.0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2318.80</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -581,38 +603,44 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TACO MENSULA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>1050</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>1050.0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>1302.00</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -627,38 +655,44 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TACO PISO</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>1200</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>1200.0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>1488.00</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -673,38 +707,44 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TACO ANTIVIBRATORIO CUADRADO</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>132</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>163.68</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -719,38 +759,44 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TACO GOMA ANTIVIBRATORIO</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>112</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>112.0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>138.88</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -765,38 +811,44 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>ANTIVIBRATORIO (ELIMINA EL 100% VIBRACION) x unidad</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>880</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>880.0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>1091.20</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -811,38 +863,44 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>SOPORTE PARA UNIDAD CONDENSADORA x4</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>2674</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>2674.0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>3315.76</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -857,38 +915,44 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>Patas originales de motor de heladera</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>275</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>275.0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>341.00</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -903,38 +967,44 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>AISLACION 1/4 x 6mm x 1,83</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>586</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>586.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>726.64</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -949,38 +1019,44 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>AISLACION 3/8 x 6mm x 1,83</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>758</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>758.0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>939.92</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -995,38 +1071,44 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>AISLACION 1/2 x 6mm x 1,83</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>887</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>887.0</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>1099.88</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1041,38 +1123,44 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>AISLACION 5/8 x 6mm x 1,83</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>1058</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>1058.0</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>1311.92</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1087,38 +1175,44 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>DREAN 166 JUEGO X3</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>2860</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>2860.0</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>3546.40</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1133,38 +1227,44 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TORNILLO DREAN BLUE ORIGINAL</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>400</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>400.0</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>496.00</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1179,38 +1279,44 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TORNILLO ALLEN GRANDE ELECTROLUX Y SAMSUNG</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>429</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>429.0</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>531.96</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1225,38 +1331,44 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>RULEMAN 6203 zrs (con goma y caja)</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2548</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>2548.0</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>3159.52</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1271,38 +1383,44 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>RULEMAN 6204 zrs (con goma)</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>3350</v>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>3350.0</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>4154.00</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1317,38 +1435,44 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>RULEMAN 6205 zrs (con goma)</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>3960</v>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>3960.0</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>4910.40</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1363,38 +1487,44 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>RULEMAN 6206 zrs (con goma)</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>5656</v>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>5656.0</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>7013.44</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1409,38 +1539,44 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>FORZADOR (5w) 100% cobre</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>8437</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>8437.0</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>10461.88</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1455,38 +1591,44 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>FORZADOR (10w)  100% cobre</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>10439</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>10439.0</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>12944.36</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1501,38 +1643,44 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>FORZADOR (16w) 100% cobre</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>14729</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>14729.0</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>18263.96</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1547,38 +1695,44 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>FORZADOR (18w) 100% cobre</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>16159</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>16159.0</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>20037.16</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1593,38 +1747,44 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>FORZADOR (25w) 100% cobre</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>18590</v>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>18590.0</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>23051.60</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1639,38 +1799,44 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>FORZADOR (34w) 100% cobre</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>20020</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
           <t>20020.0</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>24824.80</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1685,38 +1851,44 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Soporte auxiliar para unidad interior (precio por conjunto de 2 soportes)</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>19800</v>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>19800.0</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>24552.00</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1731,38 +1903,44 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>CAJA DE PREINSTALACIÓN</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>1400</v>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1400.0</t>
+          <t>ARS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
           <t>1736.00</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1777,38 +1955,44 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>CINTA SIN ADHESIVO</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>1144</v>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>1144.0</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>1418.56</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1823,38 +2007,44 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>CAJA ESTANCA 9X9</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>550</v>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>550.0</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>682.00</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1869,38 +2059,44 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>TAPA SALIDA EXTERIOR</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>1430</v>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>1430.0</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>1773.20</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1915,38 +2111,44 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Tarugos del 6 con tornillos y arandelas (6 unidades)</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>308</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>308.0</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>381.92</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -1961,38 +2163,44 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Tarugos del 10 con tornillos y arandelas (6 unidades)</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>1045</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>1045.0</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>1295.80</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2007,38 +2215,44 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>MANTA IGNIFUGA 10mm de espesor(25cm x 30cm)</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>6435</v>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>6435.0</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>7979.40</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2053,38 +2267,44 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>Soporte unidad interior conjuntox2 unidades con regulacion</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>3960</v>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>3960.0</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>4910.40</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2099,38 +2319,44 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>SENSOR DE HELADERA 2,7K</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>1859</v>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>1859.0</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>2305.16</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2145,38 +2371,44 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>SENSOR DE HELADERA 5K</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>1859</v>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>1859.0</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>2305.16</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2191,38 +2423,44 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>SENSOR DE HELADERA 10K</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>1859</v>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>1859.0</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2305.16</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2237,38 +2475,44 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>SENSORES DE AIRE 5K</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>2288</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>2288.0</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>2837.12</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2283,38 +2527,44 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>SENSORES DE AIRE 10K</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="F41" t="n">
         <v>2288</v>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>2288.0</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>2837.12</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2329,38 +2579,44 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>SENSORES DE AIRE 15K</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
         <v>2288</v>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>2288.0</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>2837.12</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2375,38 +2631,44 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>TERMOFUSIBLE WHIRPOOL</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="F43" t="n">
         <v>3289</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>3289.0</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>4078.36</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2421,38 +2683,44 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>BIMETAL CON FUSIBLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
         <v>3718</v>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>3718.0</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>4610.32</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2467,38 +2735,44 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>BIMETAL DE HELADERA</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
         <v>3718</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>3718.0</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>4610.32</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2513,38 +2787,44 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>CONTROL REMOTO UNIVERSAL</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>1573</v>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>1573.0</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>1950.52</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2559,38 +2839,44 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>CAJA TÉRMICA PARA 1</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="F47" t="n">
         <v>660</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>660.0</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>818.40</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2605,38 +2891,44 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>CAJA TÉRMICA PARA 2 o 1 y ENCHUFE</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="F48" t="n">
         <v>990</v>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>990.0</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>1227.60</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2651,38 +2943,44 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>PATA HELADERA COMERCIAL 9cm</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>275</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>275.0</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>341.00</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2697,38 +2995,44 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>TARUGO PARA PRECINTO 8 (SUPERTARUGO)</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>13</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>13.0</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>16.12</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2743,38 +3047,44 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>CRISTAL  DE 5/8, 0% FACTURADA, rollo x25 metros</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
         <v>12870</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>12870.0</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>15958.80</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2789,38 +3099,44 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>UNION PARA MANGUERA DE 5/8</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
         <v>132</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>163.68</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2835,38 +3151,44 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Codo a 90°</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
         <v>132</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>163.68</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2881,38 +3203,44 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Y PARA MANGUERA CRISTAL DE 5/8</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
         <v>132</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G54" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>163.68</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2927,38 +3255,44 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>PICO DESAGOTE UNIVERSAL</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>264</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>264.0</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>327.36</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -2973,38 +3307,44 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>presostato (de alta, 410)aire acondicionado Emerson</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="F56" t="n">
         <v>11000</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>11000.0</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>13640.00</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3019,38 +3359,44 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>PALETA 3 ASPAS (40,8cm)</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="F57" t="n">
         <v>8075</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>8075.0</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>10013.00</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3065,38 +3411,44 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>PALETA 4 ASPAS (40,8cm)</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>9922</v>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>9922.0</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>12303.28</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3111,38 +3463,44 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>PALETA FORZADOR (200mm)</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>1316</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>1316.0</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>1631.84</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3157,38 +3515,44 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>PALETA FORZADOR (230mm)</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
         <v>2002</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G60" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>2002.0</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>2482.48</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3203,38 +3567,44 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>PALETA FORZADOR (250mm)</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="F61" t="n">
         <v>2116</v>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>2116.0</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>2623.84</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3249,38 +3619,44 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>PALETA FORZADOR (300mm)</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>3375</v>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G62" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
           <t>3375.0</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>4185.00</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3295,38 +3671,44 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>VALVULA CHECK 1/4</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
         <v>1430</v>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G63" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>1430.0</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>1773.20</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3341,38 +3723,44 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>COMPRESOR INVERTER 410, 2250 frigorias</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="F64" t="n">
         <v>110000</v>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>110000.0</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>136400.00</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3387,38 +3775,44 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>COMPRESOR INVERTER 410, 3000 frigorias</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="F65" t="n">
         <v>110000</v>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G65" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
           <t>110000.0</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>136400.00</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3433,38 +3827,44 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>cerigrafia + plaqueta</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="F66" t="n">
         <v>38500</v>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
           <t>38500.0</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>47740.00</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3479,38 +3879,44 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>VALVULA INVERSORA 3/8 (sin bobina)</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="F67" t="n">
         <v>12100</v>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>12100.0</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>15004.00</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3525,38 +3931,44 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Válvula lavarropa whirpool</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="F68" t="n">
         <v>6000</v>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G68" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>6000.0</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>7440.00</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3571,38 +3983,44 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Display Heladera Siam Fcx-320xt</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>15000</v>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>15000.0</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>18600.00</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3617,38 +4035,44 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Cinta scotch transparente 48x100 metros</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="F70" t="n">
         <v>1100</v>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
           <t>1100.0</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>1364.00</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3663,38 +4087,44 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>Motor</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="F71" t="n">
         <v>3500</v>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
           <t>3500.0</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>4340.00</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3709,38 +4139,44 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
           <t>UNIDAD EXTERIOR FRIO SOLO 2250, 410</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="F72" t="n">
         <v>250000</v>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
           <t>250000.0</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>310000.00</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3755,38 +4191,44 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>Electrovalvula philco</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="F73" t="n">
         <v>7000</v>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
           <t>7000.0</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>8680.00</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3801,38 +4243,44 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>SWITCH PHILCO</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="F74" t="n">
         <v>2000</v>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G74" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
           <t>2000.0</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>2480.00</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3847,38 +4295,44 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>AGITADOR PHILCO (ORIGINAL)</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>20000</v>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
           <t>20000.0</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>24800.00</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3893,38 +4347,44 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
           <t>Electrovalvula</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="F76" t="n">
         <v>8000</v>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
           <t>8000.0</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>9920.00</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3939,38 +4399,44 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>Cerigrafia philco 708</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>2500</v>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
           <t>2500.0</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>3100.00</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -3985,38 +4451,44 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>Valvula desagote philco</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="F78" t="n">
         <v>8500</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
           <t>8500.0</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>10540.00</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4031,38 +4503,44 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
           <t>CARCASA+JABONERA Y CABLEADO SAMSUNG WA70/80</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="F79" t="n">
         <v>30000</v>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
           <t>30000.0</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>37200.00</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4077,38 +4555,44 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>Plaqueta heladera siam Hft4310x</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>40000</v>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
           <t>40000.0</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>49600.00</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4123,38 +4607,44 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>Filtro de lavarropa</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="F81" t="n">
         <v>1000</v>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G81" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
           <t>1000.0</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>1240.00</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4169,38 +4659,44 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Motor philco xdt-180</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>50000</v>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
           <t>50000.0</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>62000.00</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4215,38 +4711,44 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>Motor secarropa</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
         <v>65000</v>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
           <t>65000.0</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>80600.00</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4261,38 +4763,44 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>Turbina siam</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
         <v>20000</v>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G84" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
           <t>20000.0</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>24800.00</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4307,38 +4815,44 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
           <t>Emerson XWB300D</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="F85" t="n">
         <v>400000</v>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
           <t>400000.0</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>496000.00</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4353,38 +4867,44 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Termostato 16e09-101</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="F86" t="n">
         <v>76000</v>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G86" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
           <t>76000.0</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>94240.00</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4399,38 +4919,44 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>Controlador dixell. 6 relay XC46OD</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>320000</v>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G87" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
           <t>320000.0</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>396800.00</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4445,38 +4971,44 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
           <t>Calentador de carter 918 0028 01</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="F88" t="n">
         <v>79200</v>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G88" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
           <t>79200.0</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>98208.00</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4491,38 +5023,44 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
           <t>Dixell Emerson XMM669K-5N1CO</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="F89" t="n">
         <v>280000</v>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G89" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
           <t>280000.0</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>347200.00</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4537,38 +5075,44 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>Zr28k5e tfd 600 (22-2,5HP)</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="F90" t="n">
         <v>643500</v>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
           <t>643500.0</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>797940.00</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4583,38 +5127,44 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Zr28k3 pfj 522 (22-2,5HP)</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>643500</v>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
           <t>643500.0</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>797940.00</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4629,38 +5179,44 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Zr28k3 tfd 522 (22-2,5HP)</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>643500</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G92" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
           <t>643500.0</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>797940.00</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4675,38 +5231,44 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
           <t>Zr30k3 pfj 522 (22-3HP)</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="F93" t="n">
         <v>643500</v>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G93" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
           <t>643500.0</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>797940.00</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4721,38 +5283,44 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Zr30k3 tfd 130 (22-3HP)</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="F94" t="n">
         <v>643500</v>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G94" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
           <t>643500.0</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>797940.00</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4767,38 +5335,44 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>Zr 47k3 pfj 522 (22-4HP)</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="F95" t="n">
         <v>759330</v>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
           <t>759330.0</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>941569.20</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4813,38 +5387,44 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>Zr61 ke tfd 52e (22-5HP)</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="F96" t="n">
         <v>707850</v>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G96" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
           <t>707850.0</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>877734.00</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4859,38 +5439,44 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>Zr81 kc tfd 430 (22-6,5HP)</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="F97" t="n">
         <v>965250</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
           <t>965250.0</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>1196910.00</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4905,38 +5491,44 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Zr144kce tfd 550 (22-12HP)</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="F98" t="n">
         <v>2574000</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
           <t>2574000.0</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>3191760.00</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4951,38 +5543,44 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Zr144 kc tfd 551 (22-12HP)</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="F99" t="n">
         <v>2059200</v>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G99" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
           <t>2059200.0</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>2553408.00</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -4997,38 +5595,44 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
           <t>Zr160 kce tfd 568 (22-13HP)</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>2574000</v>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G100" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
           <t>2574000.0</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>3191760.00</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5043,38 +5647,44 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
           <t>Zp24k5e tfd 662 (410-2HP)</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="F101" t="n">
         <v>836550</v>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
           <t>836550.0</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>1037322.00</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5089,38 +5699,44 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
           <t>Zp61kcetfd 622 (410-5HP)</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>965250</v>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G102" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
           <t>965250.0</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>1196910.00</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5135,38 +5751,44 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>Zp83kce tfd 522  (410-7HP)</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="F103" t="n">
         <v>1544400</v>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
           <t>1544400.0</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>1915056.00</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5181,38 +5803,44 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>Zp104 kce tfd 550 (410-9HP)</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="F104" t="n">
         <v>2187900</v>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
           <t>2187900.0</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>2712996.00</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5227,38 +5855,44 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>Zb19 kce tfd 551</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="F105" t="n">
         <v>1784640</v>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G105" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
           <t>1784640.0</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>2212953.60</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5273,38 +5907,44 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
           <t>Zb26kcetfd 551</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="F106" t="n">
         <v>2059200</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G106" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
           <t>2059200.0</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>2553408.00</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5319,38 +5959,44 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>Zb30kce tfd 551</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="F107" t="n">
         <v>3217500</v>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G107" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
           <t>3217500.0</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>3989700.00</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5365,38 +6011,44 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>Zb38 kc tfd 551</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="F108" t="n">
         <v>2123550</v>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G108" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
           <t>2123550.0</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>2633202.00</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5411,38 +6063,44 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>Zf18k4e tfd 551</t>
         </is>
       </c>
-      <c r="D109" t="n">
+      <c r="F109" t="n">
         <v>3861000</v>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G109" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
           <t>3861000.0</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>4787640.00</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5457,38 +6115,44 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>Zb48 kce tfd 551</t>
         </is>
       </c>
-      <c r="D110" t="n">
+      <c r="F110" t="n">
         <v>2895750</v>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G110" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
           <t>2895750.0</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>3590730.00</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5503,38 +6167,44 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
           <t>Zf09k4etfd 551</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="F111" t="n">
         <v>3377660</v>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G111" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
           <t>3377660.0</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>4188298.40</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5549,38 +6219,44 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
           <t>Zf25kqe tfd 551</t>
         </is>
       </c>
-      <c r="D112" t="n">
+      <c r="F112" t="n">
         <v>4979260</v>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G112" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
           <t>4979260.0</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>6174282.40</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5595,38 +6271,44 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>Zb15kce tfd 551</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="F113" t="n">
         <v>1673100</v>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G113" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
           <t>1673100.0</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>2074644.00</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5641,38 +6323,44 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Zs09 kae pfj 600</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="F114" t="n">
         <v>939510</v>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G114" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
           <t>939510.0</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>1164992.40</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5687,38 +6375,44 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
           <t>Zs13 kae tfd 600</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="F115" t="n">
         <v>1158300</v>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G115" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
           <t>1158300.0</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>1436292.00</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5733,38 +6427,44 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
           <t>Zf11k4e tfd 551</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="F116" t="n">
         <v>3603600</v>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G116" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
           <t>3603600.0</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>4468464.00</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5779,38 +6479,44 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
           <t>Zf 15 k4e tfd 551</t>
         </is>
       </c>
-      <c r="D117" t="n">
+      <c r="F117" t="n">
         <v>3732300</v>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G117" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
           <t>3732300.0</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>4628052.00</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5825,38 +6531,44 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>Zs15kae pfj600</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="F118" t="n">
         <v>1132560</v>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G118" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
           <t>1132560.0</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>1404374.40</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5871,38 +6583,44 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
           <t>Zs19kae tfj 600</t>
         </is>
       </c>
-      <c r="D119" t="n">
+      <c r="F119" t="n">
         <v>1158300</v>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G119" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
           <t>1158300.0</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>1436292.00</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5917,38 +6635,44 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
           <t>Zs26kaepfj 600</t>
         </is>
       </c>
-      <c r="D120" t="n">
+      <c r="F120" t="n">
         <v>1415700</v>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G120" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
           <t>1415700.0</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>1755468.00</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -5963,38 +6687,44 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
           <t>Zs38 k4e tfd 551</t>
         </is>
       </c>
-      <c r="D121" t="n">
+      <c r="F121" t="n">
         <v>1847560</v>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G121" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
           <t>1847560.0</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>2290974.40</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
@@ -6009,38 +6739,44 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
+          <t>wholesale</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
           <t>Tuerca de refrigeracion 1/2</t>
         </is>
       </c>
-      <c r="D122" t="n">
+      <c r="F122" t="n">
         <v>1850</v>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>ARS</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
       <c r="G122" t="inlineStr">
         <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
           <t>1850.0</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="J122" t="inlineStr">
         <is>
           <t>2294.00</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>skipped</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>skipped</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
         <is>
           <t>Missing code</t>
         </is>
